--- a/examples/MPG-min-num.xlsx
+++ b/examples/MPG-min-num.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhv/git/pythmpg/git/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0606B31-C477-3D42-93C1-8CDFC00A644E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B2422-F62C-6447-8CAC-26875B749DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="1100" windowWidth="20260" windowHeight="12460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -966,13 +966,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1367,7 +1364,7 @@
       </c>
       <c r="W1" s="21"/>
     </row>
-    <row r="2" spans="1:1024" ht="41.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1024" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1543,13 +1540,13 @@
       <c r="AMJ4" s="13"/>
     </row>
     <row r="5" spans="1:1024" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <f>COUNTIF(A6:A127, "&lt;&gt;")</f>
         <v>122</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
       <c r="E5" s="15"/>
       <c r="F5" s="1">
         <f>COUNTIF(F6:F127,"&gt;0")</f>
